--- a/artfynd/A 46893-2021 artfynd.xlsx
+++ b/artfynd/A 46893-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46893-2021 artfynd.xlsx
+++ b/artfynd/A 46893-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62756520</v>
+        <v>56755177</v>
       </c>
       <c r="B2" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -720,14 +715,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grytterud, SV om vid väg S529, Vrm</t>
+          <t>Grytterud, väg S529, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>363525.928268085</v>
+        <v>363526</v>
       </c>
       <c r="R2" t="n">
-        <v>6563645.90181698</v>
+        <v>6563646</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,29 +747,14 @@
           <t>Svanskog</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>S-Säf-0281</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
           <t>2013-07-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-07-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,17 +774,385 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>John Rolander Borlid</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Åsa Röstell, Tove Adelsköld</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>118011446</v>
+      </c>
+      <c r="B3" t="n">
+        <v>107908</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Grytterud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>363644</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6563645</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Svanskog</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ett bestånd står i vägområdet, står i ytterslänt. Även ett bestånd utanför vägområdet. Norra sidan vägen</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>victoria höglund</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>victoria höglund, Oscar Hallberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>102225721</v>
+      </c>
+      <c r="B4" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ängen, N om, svinrot, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>363495</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6563636</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Svanskog</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>S-Säf-0534</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Nyetablering efter dikesrensning för ett par år sedan. Norra sidan av vägen.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Owe Nilsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>Åsa Röstell, Tove Adelsköld</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118011613</v>
+      </c>
+      <c r="B5" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Grytterud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>363511</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6563638</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Svanskog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Innerslänt norra sidan vägen</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>victoria höglund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>victoria höglund, Oscar Hallberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 46893-2021 artfynd.xlsx
+++ b/artfynd/A 46893-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56755177</t>
         </is>
       </c>
     </row>
@@ -907,6 +917,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118011446</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1033,6 +1048,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102225721</t>
         </is>
       </c>
     </row>
@@ -1155,8 +1175,19 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118011613</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>